--- a/cds_files/TCU_CDS_2022-2023.xlsx
+++ b/cds_files/TCU_CDS_2022-2023.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.96</v>
+        <v>0.952</v>
       </c>
       <c r="C3" t="n">
-        <v>0.48</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04</v>
+        <v>0.048</v>
       </c>
       <c r="C4" t="n">
-        <v>0.52</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="5">
